--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/5278-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/5278-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{327A63DA-8E88-41BB-9775-EBECF1C1487F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7510B987-7F84-4C4B-A515-859B0EB7C34F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{669F85E3-694A-4461-825C-74B22BB0BBFB}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{1D5D3DC4-73C7-4D45-8AC0-316C5F1013A4}"/>
   </bookViews>
   <sheets>
     <sheet name="5278-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1576,28 +1576,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC2B7691-9E99-4668-913C-8A2D364581FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0F8E30D-8ED0-4120-98CF-50B32073C76A}">
   <dimension ref="A1:X46"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="8.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.125" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="7" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1631,7 +1631,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1667,7 +1667,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1787,7 +1787,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39"/>
       <c r="B6" s="40"/>
       <c r="C6" s="42"/>
@@ -1895,7 +1895,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -2043,7 +2043,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>29</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="47">
         <v>2024</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>2.72</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>29</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
         <v>29</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>29</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="49">
         <v>2023</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>29</v>
       </c>
@@ -2631,7 +2631,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>8.98</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2779,7 +2779,7 @@
         <v>1.41</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2853,7 +2853,7 @@
         <v>1.67</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="47">
         <v>2022</v>
       </c>
@@ -2925,7 +2925,7 @@
         <v>6.43</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
         <v>29</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>1.63</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
         <v>29</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
         <v>29</v>
       </c>
@@ -3147,7 +3147,7 @@
         <v>2.13</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
         <v>29</v>
       </c>
@@ -3221,7 +3221,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="49">
         <v>2021</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>29</v>
       </c>
@@ -3367,7 +3367,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>29</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>29</v>
       </c>
@@ -3515,7 +3515,7 @@
         <v>3.01</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>29</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="47">
         <v>2020</v>
       </c>
@@ -3661,7 +3661,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="18" t="s">
         <v>29</v>
       </c>
@@ -3735,7 +3735,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="18" t="s">
         <v>29</v>
       </c>
@@ -3809,7 +3809,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="18" t="s">
         <v>29</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>3.14</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="18" t="s">
         <v>29</v>
       </c>
@@ -3957,7 +3957,7 @@
         <v>3.01</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="49">
         <v>2019</v>
       </c>
@@ -4029,7 +4029,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
         <v>29</v>
       </c>
@@ -4103,7 +4103,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
         <v>29</v>
       </c>
@@ -4177,7 +4177,7 @@
         <v>1.88</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
         <v>29</v>
       </c>
@@ -4251,7 +4251,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="47">
         <v>2018</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>8.99</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="49">
         <v>2017</v>
       </c>
@@ -4395,7 +4395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="47">
         <v>2016</v>
       </c>
@@ -4467,7 +4467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="49">
         <v>2015</v>
       </c>
@@ -4539,7 +4539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="47">
         <v>2014</v>
       </c>
@@ -4611,7 +4611,7 @@
         <v>4.97</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="49">
         <v>2013</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="47">
         <v>2012</v>
       </c>
@@ -4755,7 +4755,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="49" t="s">
         <v>65</v>
       </c>
